--- a/artfynd/A 13142-2026 artfynd.xlsx
+++ b/artfynd/A 13142-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,7 +682,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -795,6 +795,129 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134448211</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58466</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103074</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tajgablåstjärt</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tarsiger cyanurus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Höglidmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>621348</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7209766</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Per Samuelson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Per Samuelson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13142-2026 artfynd.xlsx
+++ b/artfynd/A 13142-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,130 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134590594</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58466</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103074</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tajgablåstjärt</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tarsiger cyanurus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1773)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Höglidmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>621385</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7209758</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>20:58</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hördes från vändplanen</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Tranderyd</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Tranderyd, Markus Eriksson Nordkvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13142-2026 artfynd.xlsx
+++ b/artfynd/A 13142-2026 artfynd.xlsx
@@ -708,18 +708,18 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Höglidmyran, Ly lm</t>
@@ -772,6 +772,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>10:45</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sjungande i högvuxen fuktig tät blandskog</t>
         </is>
       </c>
       <c r="AD2" t="b">
